--- a/Curs Oficial/sesiuni/s05/echipa_verde/Vanzari.xlsx
+++ b/Curs Oficial/sesiuni/s05/echipa_verde/Vanzari.xlsx
@@ -422,22 +422,6 @@
           <t>Export vanzari · ERP FarmPlus</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -445,22 +429,6 @@
           <t>Include retururi marcate Anulat</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +578,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -671,13 +638,11 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>143</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>16</v>
       </c>
@@ -730,7 +695,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -793,7 +757,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -856,7 +819,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -919,7 +881,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -980,7 +941,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1041,7 +1001,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1104,7 +1063,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1165,7 +1123,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1226,7 +1183,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1287,7 +1243,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1348,7 +1303,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1411,7 +1365,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,7 +1425,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1533,7 +1485,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1594,7 +1545,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1657,7 +1607,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1718,7 +1667,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1779,7 +1727,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1840,7 +1787,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1901,7 +1847,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1962,7 +1907,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2025,7 +1969,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2088,7 +2031,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2149,7 +2091,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2210,7 +2151,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2271,7 +2211,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2332,7 +2271,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2393,7 +2331,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2454,7 +2391,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2515,7 +2451,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2578,7 +2513,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2641,7 +2575,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2702,7 +2635,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2763,7 +2695,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2824,7 +2755,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2885,7 +2815,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2946,7 +2875,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3009,7 +2937,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3070,7 +2997,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3131,7 +3057,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3194,7 +3119,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3257,7 +3181,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3318,7 +3241,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3379,7 +3301,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3440,7 +3361,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3503,7 +3423,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3566,7 +3485,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3627,7 +3545,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3688,7 +3605,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3749,27 +3665,8 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" t="n">
         <v>299</v>
@@ -3829,7 +3726,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3890,7 +3786,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3951,7 +3846,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4012,7 +3906,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4075,7 +3968,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4083,22 +3975,6 @@
           <t>SUBTOTAL ZILNIC</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4159,7 +4035,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4220,7 +4095,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4281,7 +4155,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4342,7 +4215,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4403,7 +4275,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4464,7 +4335,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4525,7 +4395,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4586,7 +4455,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4649,7 +4517,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4710,7 +4577,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4771,7 +4637,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4832,7 +4697,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4893,7 +4757,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4956,7 +4819,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5017,7 +4879,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5078,7 +4939,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5139,7 +4999,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5200,7 +5059,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5261,7 +5119,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5322,7 +5179,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5383,7 +5239,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5444,7 +5299,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5507,7 +5361,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5568,7 +5421,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5629,7 +5481,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5690,7 +5541,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5751,7 +5601,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5812,7 +5661,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5873,7 +5721,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5934,7 +5781,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5997,7 +5843,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6058,7 +5903,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6121,7 +5965,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6182,7 +6025,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6243,7 +6085,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6304,7 +6145,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6365,7 +6205,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6428,7 +6267,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6489,7 +6327,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6552,7 +6389,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6613,7 +6449,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6676,7 +6511,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6737,7 +6571,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6798,7 +6631,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6859,7 +6691,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6920,7 +6751,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6981,7 +6811,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7044,7 +6873,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7105,7 +6933,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7168,7 +6995,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7231,7 +7057,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7292,7 +7117,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7357,7 +7181,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7420,7 +7243,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7485,7 +7307,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7546,7 +7367,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7607,7 +7427,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7672,7 +7491,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7733,7 +7551,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7794,7 +7611,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7855,7 +7671,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7916,7 +7731,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7977,7 +7791,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8038,7 +7851,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8099,7 +7911,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8160,7 +7971,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8221,7 +8031,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8282,7 +8091,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8343,7 +8151,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8404,7 +8211,6 @@
           <t>RON</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8412,22 +8218,6 @@
           <t>Total linii export: 128</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
